--- a/sheets/real-estate/short-term-rental-revenue-estimator/short-term-rental-revenue-estimator.xlsx
+++ b/sheets/real-estate/short-term-rental-revenue-estimator/short-term-rental-revenue-estimator.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A08615-2D6C-4808-8410-419EE8F81AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Property &amp; Assumptions" sheetId="1" r:id="rId1"/>
@@ -561,15 +561,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC8E6C9"/>
-          <bgColor rgb="FFC8E6C9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -591,14 +583,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFE0B2"/>
           <bgColor rgb="FFFFE0B2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC8E6C9"/>
-          <bgColor rgb="FFC8E6C9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2949,10 +2933,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q2:Q13">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3349,23 +3333,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>B30&gt;C30</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>AND(ISNUMBER(B42),B43&gt;B42)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>AND(ISNUMBER(B42),B43&lt;=B42,B43&gt;=B42-0.05)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="13">
+    <cfRule type="expression" dxfId="1" priority="13">
       <formula>AND(ISNUMBER(B42),B43&lt;B42-0.05)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:C33">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>C30&gt;B30</formula>
     </cfRule>
   </conditionalFormatting>
